--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486859_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486859_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6882</v>
+        <v>2.3126</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.9005</v>
+        <v>-2.1872</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5887</v>
+        <v>4.4998</v>
       </c>
       <c r="G2" t="n">
         <v>-2.0281</v>
@@ -610,13 +610,13 @@
         <v>3.2855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.2877</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0468</v>
+        <v>-0.3334</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1347</v>
+        <v>0.0457</v>
       </c>
       <c r="V2" t="n">
         <v>2.575</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5075</v>
+        <v>2.3015</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4337</v>
+        <v>-0.1358</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9412</v>
+        <v>2.4373</v>
       </c>
       <c r="G3" t="n">
         <v>0.0537</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2506</v>
+        <v>0.5434</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.7708</v>
+        <v>-0.4729</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5203</v>
+        <v>1.0163</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3491</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1061</v>
+        <v>2.0688</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.72</v>
+        <v>-0.1427</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8261</v>
+        <v>2.2115</v>
       </c>
       <c r="G4" t="n">
         <v>2.5192</v>
@@ -766,13 +766,13 @@
         <v>3.2855</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2077</v>
+        <v>-0.2451</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8758</v>
+        <v>-0.2986</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3319</v>
+        <v>0.0535</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2792</v>
+        <v>-0.1927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2403</v>
+        <v>0.2675</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5195</v>
+        <v>-0.4602</v>
       </c>
       <c r="G5" t="n">
         <v>0.5733</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1208</v>
+        <v>0.2073</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4416</v>
+        <v>0.4687</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3207</v>
+        <v>-0.2615</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1786</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0094</v>
+        <v>-1.3951</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2316</v>
+        <v>-1.8248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2222</v>
+        <v>0.4297</v>
       </c>
       <c r="G6" t="n">
         <v>-0.625</v>
@@ -922,13 +922,13 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5281</v>
+        <v>0.0862</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.527</v>
+        <v>-0.1202</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0011</v>
+        <v>0.2064</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2402</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.751</v>
+        <v>-2.4232</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4563</v>
+        <v>-0.2471</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2947</v>
+        <v>-2.1761</v>
       </c>
       <c r="G7" t="n">
         <v>0.4416</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3898</v>
+        <v>-0.062</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3294</v>
+        <v>-0.1202</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0604</v>
+        <v>0.0581</v>
       </c>
       <c r="V7" t="n">
         <v>-2.5975</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2128</v>
+        <v>-2.9765</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5051</v>
+        <v>-4.9572</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7077</v>
+        <v>1.9808</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7222</v>
+        <v>-0.4632</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.362</v>
+        <v>-0.4214</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3602</v>
+        <v>-0.0418</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8967000000000001</v>
+        <v>0.5569</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2783</v>
+        <v>0.4385</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.1184</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8255</v>
+        <v>-1.0201</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0837</v>
+        <v>-0.8599</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7418</v>
+        <v>-0.1602</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-4.3122</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3468</v>
+        <v>0.0329</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0272</v>
+        <v>-0.5038</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3196</v>
+        <v>0.5367</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3491</v>
+        <v>-0.6982</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3491</v>
+        <v>-0.6982</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9021</v>
+        <v>-3.142</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.705</v>
+        <v>-2.5826</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8029</v>
+        <v>-0.5595</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4632</v>
+        <v>-2.7222</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4214</v>
+        <v>-1.362</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0418</v>
+        <v>-1.3602</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5569</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4385</v>
+        <v>-0.2783</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1184</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0201</v>
+        <v>-1.8255</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8599</v>
+        <v>-1.0837</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1602</v>
+        <v>-0.7418</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.3122</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8927</v>
+        <v>-0.2761</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2516</v>
+        <v>-0.1047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3589</v>
+        <v>-0.1714</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6982</v>
+        <v>-0.3491</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6982</v>
+        <v>-0.3491</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9549</v>
+        <v>-4.0876</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.4544</v>
+        <v>-6.4389</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4995</v>
+        <v>2.3513</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5624</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.7952</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0191</v>
+        <v>0.0347</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5851</v>
+        <v>-5.5528</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2945</v>
+        <v>-3.9066</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2906</v>
+        <v>-1.6463</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1603</v>
@@ -1312,13 +1312,13 @@
         <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8976</v>
+        <v>0.9298</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8405</v>
+        <v>0.2284</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0571</v>
+        <v>0.7014</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7063</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.3927</v>
+        <v>-13.087</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.4608</v>
+        <v>-22.1554</v>
       </c>
       <c r="F12" t="n">
-        <v>9.068099999999999</v>
+        <v>9.068299999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-6.9734</v>
@@ -1390,13 +1390,13 @@
         <v>18.4809</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5814999999999999</v>
+        <v>1.7239</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.527400000000001</v>
+        <v>-1.222</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9461</v>
+        <v>2.9458</v>
       </c>
       <c r="V12" t="n">
         <v>-5.784200000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9493</v>
+        <v>6.1612</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0673</v>
+        <v>3.7535</v>
       </c>
       <c r="F13" t="n">
-        <v>2.882</v>
+        <v>2.4077</v>
       </c>
       <c r="G13" t="n">
         <v>2.7694</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4119</v>
+        <v>0.6239</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4416</v>
+        <v>0.1278</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.4961</v>
       </c>
       <c r="V13" t="n">
         <v>2.3573</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1496</v>
+        <v>4.3885</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4394</v>
+        <v>1.6486</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7102</v>
+        <v>2.7399</v>
       </c>
       <c r="G14" t="n">
         <v>3.6982</v>
@@ -1546,13 +1546,13 @@
         <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8093</v>
+        <v>-0.5705</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8563</v>
+        <v>-0.6471</v>
       </c>
       <c r="U14" t="n">
-        <v>0.047</v>
+        <v>0.0766</v>
       </c>
       <c r="V14" t="n">
         <v>1.8768</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5339</v>
+        <v>3.1824</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4539</v>
+        <v>1.0815</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.1009</v>
       </c>
       <c r="G15" t="n">
         <v>1.748</v>
@@ -1624,13 +1624,13 @@
         <v>1.4374</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0518</v>
+        <v>0.5967</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8486</v>
+        <v>-0.221</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7968</v>
+        <v>0.8177</v>
       </c>
       <c r="V15" t="n">
         <v>1.6591</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1795</v>
+        <v>2.2946</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6576</v>
+        <v>-1.0761</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8371</v>
+        <v>3.3707</v>
       </c>
       <c r="G16" t="n">
         <v>0.5484</v>
@@ -1702,13 +1702,13 @@
         <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8632</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6778</v>
+        <v>0.2594</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1853</v>
+        <v>0.7189</v>
       </c>
       <c r="V16" t="n">
         <v>1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6227</v>
+        <v>1.94</v>
       </c>
       <c r="E17" t="n">
         <v>-1.4623</v>
       </c>
       <c r="F17" t="n">
-        <v>3.085</v>
+        <v>3.4024</v>
       </c>
       <c r="G17" t="n">
         <v>1.3724</v>
@@ -1780,13 +1780,13 @@
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>0.045</v>
+        <v>0.3623</v>
       </c>
       <c r="T17" t="n">
         <v>0.0464</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0014</v>
+        <v>0.3159</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>P. BONO SOLER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1567</v>
+        <v>1.4151</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9761</v>
+        <v>-0.7181</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1328</v>
+        <v>2.1331</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9889</v>
+        <v>0.8589</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0925</v>
+        <v>-1.0672</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.0814</v>
+        <v>1.9262</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0685</v>
+        <v>-0.315</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3393</v>
+        <v>-0.9859</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.4078</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0796</v>
+        <v>1.174</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2468</v>
+        <v>-0.0813</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3264</v>
+        <v>1.2552</v>
       </c>
       <c r="P18" t="n">
         <v>1.6427</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6117</v>
+        <v>0.092</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4066</v>
+        <v>-0.4031</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2051</v>
+        <v>0.4951</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1088</v>
+        <v>-1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BONO SOLER</t>
+          <t>E. HERRERA SAURET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9321</v>
+        <v>0.748</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0319</v>
+        <v>-1.1827</v>
       </c>
       <c r="F19" t="n">
-        <v>1.964</v>
+        <v>1.9307</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8589</v>
+        <v>0.7247</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0672</v>
+        <v>1.2458</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9262</v>
+        <v>-0.5211</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.315</v>
+        <v>0.6267</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9859</v>
+        <v>0.8244</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6709000000000001</v>
+        <v>-0.1977</v>
       </c>
       <c r="M19" t="n">
-        <v>1.174</v>
+        <v>0.098</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0813</v>
+        <v>0.4214</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2552</v>
+        <v>-0.3234</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3909</v>
+        <v>-0.1472</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7169</v>
+        <v>-0.3721</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3259</v>
+        <v>0.2249</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7825</v>
+        <v>0.6389</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5103</v>
+        <v>-1.6037</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2928</v>
+        <v>2.2426</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0536</v>
+        <v>-0.9889</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3429</v>
+        <v>2.0925</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2893</v>
+        <v>-3.0814</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0392</v>
+        <v>-1.0685</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4473</v>
+        <v>2.3393</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4081</v>
+        <v>-3.4078</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0144</v>
+        <v>0.0796</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1044</v>
+        <v>-0.2468</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1188</v>
+        <v>0.3264</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4641</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5236</v>
+        <v>0.0939</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2907</v>
+        <v>-0.221</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8143</v>
+        <v>0.3149</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. HERRERA SAURET</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.211</v>
+        <v>0.3065</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6012</v>
+        <v>-2.7195</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8121</v>
+        <v>3.026</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7247</v>
+        <v>0.0536</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2458</v>
+        <v>1.3429</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5211</v>
+        <v>-1.2893</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6267</v>
+        <v>0.0392</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8244</v>
+        <v>1.4473</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1977</v>
+        <v>-1.4081</v>
       </c>
       <c r="M21" t="n">
-        <v>0.098</v>
+        <v>0.0144</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4214</v>
+        <v>-0.1044</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3234</v>
+        <v>0.1188</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.4374</v>
+        <v>-2.2588</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8481</v>
+        <v>2.4641</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6842</v>
+        <v>0.0476</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7905</v>
+        <v>-0.4999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1063</v>
+        <v>0.5475</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2174</v>
+        <v>-1.5609</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2469</v>
+        <v>-1.5607</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0295</v>
+        <v>-0.0001</v>
       </c>
       <c r="G23" t="n">
         <v>-0.008200000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1933</v>
+        <v>-0.1501</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1704</v>
+        <v>-0.1434</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0229</v>
+        <v>-0.0067</v>
       </c>
       <c r="V23" t="n">
         <v>0.2402</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.252</v>
+        <v>-2.769</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4765</v>
+        <v>-5.1627</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2245</v>
+        <v>2.3936</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4925</v>
@@ -2326,13 +2326,13 @@
         <v>2.0534</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7862</v>
+        <v>-0.3032</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1198</v>
+        <v>-0.806</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3337</v>
+        <v>0.5028</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.3927</v>
+        <v>16.0901</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.068099999999998</v>
+        <v>-9.068099999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>24.4607</v>
+        <v>25.1582</v>
       </c>
       <c r="G25" t="n">
         <v>6.973599999999999</v>
@@ -2374,13 +2374,13 @@
         <v>6.9735</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000100000000000211</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="J25" t="n">
         <v>5.372999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>7.480399999999999</v>
+        <v>7.4804</v>
       </c>
       <c r="L25" t="n">
         <v>-2.107200000000001</v>
@@ -2395,7 +2395,7 @@
         <v>2.1071</v>
       </c>
       <c r="P25" t="n">
-        <v>2.0533</v>
+        <v>2.053299999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-18.4808</v>
@@ -2404,13 +2404,13 @@
         <v>20.5341</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5814999999999997</v>
+        <v>1.2789</v>
       </c>
       <c r="T25" t="n">
         <v>-2.9459</v>
       </c>
       <c r="U25" t="n">
-        <v>3.5273</v>
+        <v>4.2248</v>
       </c>
       <c r="V25" t="n">
         <v>5.7844</v>
